--- a/data/trending_integrated_20260910_15.xlsx
+++ b/data/trending_integrated_20260910_15.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3200</v>
+        <v>3360</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+60.00%</t>
+          <t>+68.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>678</v>
+        <v>710</v>
       </c>
       <c r="F2" t="n">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="G2" t="n">
-        <v>683</v>
+        <v>716</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>927891000000</v>
+        <v>954764000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>고평가 논란 속 투자 주의 의견 및 하락 가능성 언급.</t>
+          <t>급등 후 변동성 확대. 투자자 간 의견 대립 및 신중론 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['고평가', '투자 주의', '하락 가능성']</t>
+          <t>['급등', '변동성', '스펙주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8290</v>
+        <v>8270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+45.18%</t>
+          <t>+44.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F3" t="n">
         <v>123</v>
       </c>
       <c r="G3" t="n">
-        <v>1660</v>
+        <v>1677</v>
       </c>
       <c r="H3" t="n">
         <v>1.17</v>
@@ -702,7 +702,7 @@
         <v>0.77</v>
       </c>
       <c r="O3" t="n">
-        <v>70602000000</v>
+        <v>71331000000</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -762,7 +762,7 @@
         <v>-0.22</v>
       </c>
       <c r="E4" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F4" t="n">
         <v>73</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14540</v>
+        <v>14420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+23.12%</t>
+          <t>+22.10%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.45</v>
       </c>
       <c r="E5" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F5" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G5" t="n">
-        <v>947</v>
+        <v>967</v>
       </c>
       <c r="H5" t="n">
         <v>6.09</v>
@@ -886,7 +886,7 @@
         <v>5.64</v>
       </c>
       <c r="O5" t="n">
-        <v>235041000000</v>
+        <v>241363000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 소식에 따른 원전주 테마 상승 기대감.</t>
+          <t>원전 섹터 대장주로서의 기대감. 미국 신규 원전 건설 수혜 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전주', '신규 건설', '테마 상승']</t>
+          <t>['원전', '대장주', '신규 건설']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14290</v>
+        <v>3590</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.18%</t>
+          <t>+19.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>492</v>
+        <v>79</v>
       </c>
       <c r="F6" t="n">
-        <v>271</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>598</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11990</v>
+        <v>3015</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>312362000000</v>
+        <v>28004000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,60 +994,60 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유가 급등 및 지정학적 리스크 부각에 따른 급등세 연출.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유가 급등', '지정학적 리스크', '급등세']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3565</v>
+        <v>14270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+18.24%</t>
+          <t>+19.02%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>504</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>275</v>
       </c>
       <c r="G7" t="n">
-        <v>73</v>
+        <v>614</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3015</v>
+        <v>11990</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>27629000000</v>
+        <v>315753000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1086,29 +1086,29 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
+          <t>유가 급등 및 지정학적 리스크 부각에 따른 급등세 연출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['목표가', '단기과열', '주가조작']</t>
+          <t>['유가 급등', '지정학적 리스크', '급등세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F8" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G8" t="n">
-        <v>1063</v>
+        <v>1079</v>
       </c>
       <c r="H8" t="n">
         <v>15.65</v>
@@ -1222,10 +1222,10 @@
         <v>-0.26</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
         <v>55</v>
@@ -1254,7 +1254,7 @@
         <v>4.63</v>
       </c>
       <c r="O9" t="n">
-        <v>100561000000</v>
+        <v>100850000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14350</v>
+        <v>14390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.29%</t>
+          <t>+9.60%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>120783000000</v>
+        <v>121352000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1483,39 +1483,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2070</v>
+        <v>1903</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+7.70%</t>
+          <t>+8.12%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="F12" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="G12" t="n">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>2.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1922</v>
+        <v>1760</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.51</v>
+        <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>21044000000</v>
+        <v>197364000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>새만금 소식 및 반도체 건설 관련 테마주 언급, 그러나 자전거래 의혹.</t>
+          <t>종가 급락 및 기대감 저하. 단기 반등 및 종가 배팅 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['테마주', '자전거래', '의혹']</t>
+          <t>['종가', '반등', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,46 +1568,46 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1891</v>
+        <v>3915</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+7.44%</t>
+          <t>+7.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>-1.62</v>
       </c>
       <c r="E13" t="n">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="F13" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H13" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1760</v>
+        <v>3640</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>196240000000</v>
+        <v>149059000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,29 +1638,29 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>단기 급등 후 차익 실현 매물 출회 및 추가 하락 우려.</t>
+          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['단기 급등', '차익 실현', '하락 우려']</t>
+          <t>['투기과열', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.09</v>
       </c>
       <c r="E14" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="F14" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G14" t="n">
-        <v>868</v>
+        <v>934</v>
       </c>
       <c r="H14" t="n">
         <v>11.62</v>
@@ -1714,7 +1714,7 @@
         <v>11.71</v>
       </c>
       <c r="O14" t="n">
-        <v>28241000000</v>
+        <v>33533000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신용 등급 상향 및 사업 정상화 기대감, 공매도와의 대결 언급.</t>
+          <t>신용등급 상향 및 계약 관련 긍정적 뉴스. 공매도와의 대결 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신용 등급', '사업 정상화', '공매도']</t>
+          <t>['신용등급', '계약', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14680</v>
+        <v>14620</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+7.15%</t>
+          <t>+6.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1.34</v>
       </c>
       <c r="E15" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F15" t="n">
         <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="H15" t="n">
         <v>2.89</v>
@@ -1806,7 +1806,7 @@
         <v>1.55</v>
       </c>
       <c r="O15" t="n">
-        <v>110040000000</v>
+        <v>111968000000</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신주 강세 및 외국인 수급 유입에 따른 주가 상승 기대.</t>
+          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대. 외국인 수급 긍정적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 수급', '주가 상승']</t>
+          <t>['광통신', '외국인 수급', '동반 상승']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,39 +1851,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3900</v>
+        <v>6860</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+7.14%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.62</v>
+        <v>-1.03</v>
       </c>
       <c r="E16" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>243</v>
+        <v>365</v>
       </c>
       <c r="H16" t="n">
-        <v>1.57</v>
+        <v>15.68</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3640</v>
+        <v>6430</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.19</v>
+        <v>16.71</v>
       </c>
       <c r="O16" t="n">
-        <v>147603000000</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,68 +1914,68 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
+          <t>외국인 매도세와 회사 경영진에 대한 비판적 시각이 존재하며, 로봇/반도체 관련 기대감이 일부 있으나 전반적인 분위기는 부정적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['투기과열', '6G', '광통신']</t>
+          <t>['외국인 매도', '로봇', '반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6860</v>
+        <v>2050</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+6.69%</t>
+          <t>+6.66%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.03</v>
+        <v>0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F17" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G17" t="n">
-        <v>361</v>
+        <v>292</v>
       </c>
       <c r="H17" t="n">
-        <v>15.68</v>
+        <v>0.85</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6430</v>
+        <v>1922</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>16.71</v>
+        <v>0.51</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>21203000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외국인 매도세와 회사 경영진에 대한 비판적 시각이 존재하며, 로봇/반도체 관련 기대감이 일부 있으나 전반적인 분위기는 부정적.</t>
+          <t>단기 급등 후 하락 및 거래량 부진. 테마주 수혜 기대감 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외국인 매도', '로봇', '반도체']</t>
+          <t>['단기 급등', '거래량', '테마주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1862000</v>
+        <v>1863000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+3.85%</t>
+          <t>+3.90%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F18" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G18" t="n">
-        <v>2553</v>
+        <v>2596</v>
       </c>
       <c r="H18" t="n">
         <v>50.67</v>
@@ -2082,7 +2082,7 @@
         <v>50.66</v>
       </c>
       <c r="O18" t="n">
-        <v>5194701000000</v>
+        <v>5316562000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>자사주 매입 완료 및 기관 매수 전환에 따른 주가 상승 기대.</t>
+          <t>자사주 매입 마무리 및 외국인 매수 전환 기대감. 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['자사주 매입', '기관 매수', '주가 상승']</t>
+          <t>['자사주 매입', '외국인 매수', '기대감']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F19" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G19" t="n">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="H19" t="n">
         <v>23.65</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 웨스팅하우스 지분 인수 및 미국 원전 8기 건설 '팀코리아' 관련 대형 호재 언급. JP모건 리포트 등 일부 근거 제시.</t>
+          <t>원전 관련 호재 및 웨스팅하우스 지분 인수 가능성. 긍정적 전망 우세.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['웨스팅하우스', '팀코리아', '원전']</t>
+          <t>['원전', '웨스팅하우스', '호재']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="F20" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G20" t="n">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="H20" t="n">
         <v>0.33</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>269500</v>
+        <v>270000</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.04</v>
       </c>
       <c r="E22" t="n">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F22" t="n">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G22" t="n">
-        <v>1593</v>
+        <v>1677</v>
       </c>
       <c r="H22" t="n">
         <v>46.81</v>
@@ -2450,7 +2450,7 @@
         <v>46.85</v>
       </c>
       <c r="O22" t="n">
-        <v>3171866000000</v>
+        <v>3250193000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>자사주 매입 및 배당 관련 긍정적 이슈 언급, 시장 기대감 상존.</t>
+          <t>자사주 매수 및 배당 기대감 속 정치적 발언 혼재. 약보합 마감.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주 매입', '배당', '시장 기대감']</t>
+          <t>['자사주 매수', '배당', '정치']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,31 +2495,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15640</v>
+        <v>2160</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>527</v>
+        <v>199</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>15650</v>
+        <v>2160</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>7281000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,60 +2558,60 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>반도체 공장 건설 등 수주 관련 뉴스가 있으나 주가에 미치는 영향은 미미하며, 종목에 대한 부정적인 시각과 기대감이 혼재.</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['수주', '반도체 공장', '건설']</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2135</v>
+        <v>15640</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-1.16%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.35</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="G24" t="n">
-        <v>198</v>
+        <v>546</v>
       </c>
       <c r="H24" t="n">
-        <v>4.91</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2160</v>
+        <v>15650</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>7166000000</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,29 +2650,29 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
+          <t>LH의 호남 반도체 설계 용역 발주 및 금호건설의 수주 가능성 언급. 일부 개별적인 급등 기대 및 주가 하락에 대한 불안감 혼재.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
+          <t>['반도체 설계 용역', '수주', '주가 전망']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19570</v>
+        <v>19610</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-2.00%</t>
+          <t>-1.80%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G25" t="n">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>137870000000</v>
+        <v>141602000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차 해지 운동 참여 독려 및 주가 상승 기대감 표출.</t>
+          <t>대차해지 동참 요청에도 불구하고 주가 하락. 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차 해지', '주가 상승', '기대감']</t>
+          <t>['대차해지', '주가 하락', '투자 심리']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3690</v>
+        <v>3645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-5.14%</t>
+          <t>-6.30%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H26" t="n">
         <v>1.54</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>52373000000</v>
+        <v>53129000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2878,10 +2878,10 @@
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
         <v>72</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-24.22%</t>
+          <t>-23.06%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F28" t="n">
         <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>10244000000</v>
+        <v>10399000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3062,13 +3062,13 @@
         <v>-0.32</v>
       </c>
       <c r="E29" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H29" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_15.xlsx
+++ b/data/trending_integrated_20260910_15.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3360</v>
+        <v>8180</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+68.00%</t>
+          <t>+43.26%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>710</v>
+        <v>328</v>
       </c>
       <c r="F2" t="n">
-        <v>309</v>
+        <v>122</v>
       </c>
       <c r="G2" t="n">
-        <v>716</v>
+        <v>1678</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>5710</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -607,10 +607,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>954764000000</v>
+        <v>72055000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>급등 후 변동성 확대. 투자자 간 의견 대립 및 신중론 제기.</t>
+          <t>페니트리움바이오, 폐암학회 발표 및 FDA 임상 관련 대형 재료 기대. 매물 소진 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['급등', '변동성', '스펙주']</t>
+          <t>['폐암학회', 'FDA 임상', '대형 재료']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0197V0</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8270</v>
+        <v>13030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+44.83%</t>
+          <t>+29.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4</v>
+        <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>325</v>
+        <v>131</v>
       </c>
       <c r="F3" t="n">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>1677</v>
+        <v>126</v>
       </c>
       <c r="H3" t="n">
-        <v>1.17</v>
+        <v>0.14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>5710</v>
+        <v>10030</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.77</v>
+        <v>0.36</v>
       </c>
       <c r="O3" t="n">
-        <v>71331000000</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>폐암 학회 발표 및 글로벌 제약사 협력 기대감, 임상 결과 주목.</t>
+          <t>삼미금속, 창사 이래 최대 호재 언급 있으나 구체적인 근거 제시 부족. 그래핀 신소재 관련 기대감 일부 포함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['폐암', '임상 결과', '글로벌 협력']</t>
+          <t>['그래핀', '신소재', '호재']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13030</v>
+        <v>14380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+29.91%</t>
+          <t>+21.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.22</v>
+        <v>0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="G4" t="n">
-        <v>123</v>
+        <v>999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.14</v>
+        <v>6.09</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10030</v>
+        <v>11810</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.36</v>
+        <v>5.64</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>246464000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -810,20 +810,20 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼미금속, 창사 이래 최대 호재 언급 있으나 구체적인 근거 제시 부족. 그래핀 신소재 관련 기대감 일부 포함.</t>
+          <t>우리기술, 미국 신규 원전 건설 소식 기반 상승 기대. 대장주 부각 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['그래핀', '신소재', '호재']</t>
+          <t>['원전주', '미국 신규 원전', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14420</v>
+        <v>14540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.10%</t>
+          <t>+21.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.45</v>
+        <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>189</v>
+        <v>497</v>
       </c>
       <c r="F5" t="n">
-        <v>112</v>
+        <v>275</v>
       </c>
       <c r="G5" t="n">
-        <v>967</v>
+        <v>621</v>
       </c>
       <c r="H5" t="n">
-        <v>6.09</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11810</v>
+        <v>11990</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -883,10 +883,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>241363000000</v>
+        <v>319856000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>원전 섹터 대장주로서의 기대감. 미국 신규 원전 건설 수혜 전망.</t>
+          <t>흥구석유, 유가 급등 가능성에 기반한 상승 기대. 이란 관련 지정학적 리스크 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['원전', '대장주', '신규 건설']</t>
+          <t>['유가 급등', '지정학적 리스크', '이란']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
@@ -935,18 +935,18 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3590</v>
+        <v>3615</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.07%</t>
+          <t>+19.90%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
         <v>42</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>28004000000</v>
+        <v>28509000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1023,39 +1023,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14270</v>
+        <v>12830</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+19.02%</t>
+          <t>+11.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.03</v>
+        <v>-0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>504</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>275</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>614</v>
+        <v>55</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>4.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11990</v>
+        <v>11530</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O7" t="n">
-        <v>315753000000</v>
+        <v>101161000000</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1086,29 +1086,29 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유가 급등 및 지정학적 리스크 부각에 따른 급등세 연출.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유가 급등', '지정학적 리스크', '급등세']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
@@ -1130,13 +1130,13 @@
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F8" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>1079</v>
+        <v>1088</v>
       </c>
       <c r="H8" t="n">
         <v>15.65</v>
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12720</v>
+        <v>14460</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+10.32%</t>
+          <t>+10.13%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.26</v>
+        <v>-0.53</v>
       </c>
       <c r="E9" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>55</v>
+        <v>182</v>
       </c>
       <c r="H9" t="n">
-        <v>4.37</v>
+        <v>0.57</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>11530</v>
+        <v>13130</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.63</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>100850000000</v>
+        <v>122248000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>중동 분쟁 관련 강관 수요 증가 기대감 속 주가 등락 반복, 재무제표 기반 목표가 논의.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['중동', '강관', '재무재표']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,46 +1292,46 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>092790</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14390</v>
+        <v>2185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.60%</t>
+          <t>+9.25%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>100</v>
+        <v>763</v>
       </c>
       <c r="F10" t="n">
-        <v>67</v>
+        <v>330</v>
       </c>
       <c r="G10" t="n">
-        <v>144</v>
+        <v>759</v>
       </c>
       <c r="H10" t="n">
-        <v>0.57</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13130</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>121352000000</v>
+        <v>975314000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>중동 분쟁 관련 강관 수요 증가 기대감 속 주가 등락 반복, 재무제표 기반 목표가 논의.</t>
+          <t>엔에이치스팩34호, 높은 변동성과 투자 주의 의견 다수. 단기 급등 후 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['중동', '강관', '재무재표']</t>
+          <t>['스팩주', '변동성', '주의']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,51 +1379,51 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>092790</t>
+          <t>0197V0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31100</v>
+        <v>2085</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+8.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>168</v>
+        <v>297</v>
       </c>
       <c r="H11" t="n">
-        <v>12.31</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>28750</v>
+        <v>1922</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>12.14</v>
+        <v>0.51</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>21622000000</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,60 +1454,60 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
+          <t>단기 급등 후 하락 및 거래량 부진. 테마주 수혜 기대감 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['외국인 매도', '개인 매수', '차익실현']</t>
+          <t>['단기 급등', '거래량', '테마주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1903</v>
+        <v>31100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.12%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="E12" t="n">
+        <v>88</v>
+      </c>
+      <c r="F12" t="n">
+        <v>52</v>
+      </c>
+      <c r="G12" t="n">
         <v>169</v>
       </c>
-      <c r="F12" t="n">
-        <v>98</v>
-      </c>
-      <c r="G12" t="n">
-        <v>251</v>
-      </c>
       <c r="H12" t="n">
-        <v>2.12</v>
+        <v>12.31</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1760</v>
+        <v>28750</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.07</v>
+        <v>12.14</v>
       </c>
       <c r="O12" t="n">
-        <v>197364000000</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,68 +1546,68 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>종가 급락 및 기대감 저하. 단기 반등 및 종가 배팅 가능성 언급.</t>
+          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['종가', '반등', '기대감']</t>
+          <t>['외국인 매도', '개인 매수', '차익실현']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3915</v>
+        <v>1900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+7.55%</t>
+          <t>+7.95%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.62</v>
+        <v>0.05</v>
       </c>
       <c r="E13" t="n">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="G13" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H13" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3640</v>
+        <v>1760</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.19</v>
+        <v>2.07</v>
       </c>
       <c r="O13" t="n">
-        <v>149059000000</v>
+        <v>198524000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,68 +1638,68 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
+          <t>종가 급락 및 기대감 저하. 단기 반등 및 종가 배팅 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['투기과열', '6G', '광통신']</t>
+          <t>['종가', '반등', '기대감']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7760</v>
+        <v>3915</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+7.18%</t>
+          <t>+7.55%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.09</v>
+        <v>-1.62</v>
       </c>
       <c r="E14" t="n">
-        <v>258</v>
+        <v>111</v>
       </c>
       <c r="F14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>934</v>
+        <v>246</v>
       </c>
       <c r="H14" t="n">
-        <v>11.62</v>
+        <v>1.57</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7240</v>
+        <v>3640</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>11.71</v>
+        <v>3.19</v>
       </c>
       <c r="O14" t="n">
-        <v>33533000000</v>
+        <v>150888000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,68 +1730,68 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신용등급 상향 및 계약 관련 긍정적 뉴스. 공매도와의 대결 언급.</t>
+          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신용등급', '계약', '공매도']</t>
+          <t>['투기과열', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14620</v>
+        <v>6860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+6.72%</t>
+          <t>+6.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.34</v>
+        <v>-1.03</v>
       </c>
       <c r="E15" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="G15" t="n">
-        <v>702</v>
+        <v>365</v>
       </c>
       <c r="H15" t="n">
-        <v>2.89</v>
+        <v>15.68</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>13700</v>
+        <v>6430</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1803,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.55</v>
+        <v>16.71</v>
       </c>
       <c r="O15" t="n">
-        <v>111968000000</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -1822,20 +1822,20 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대. 외국인 수급 긍정적.</t>
+          <t>외국인 매도세와 회사 경영진에 대한 비판적 시각이 존재하며, 로봇/반도체 관련 기대감이 일부 있으나 전반적인 분위기는 부정적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 수급', '동반 상승']</t>
+          <t>['외국인 매도', '로봇', '반도체']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,46 +1844,46 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6860</v>
+        <v>14590</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+6.69%</t>
+          <t>+6.50%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.03</v>
+        <v>1.34</v>
       </c>
       <c r="E16" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="G16" t="n">
-        <v>365</v>
+        <v>706</v>
       </c>
       <c r="H16" t="n">
-        <v>15.68</v>
+        <v>2.89</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6430</v>
+        <v>13700</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>16.71</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>114478000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,20 +1914,20 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>외국인 매도세와 회사 경영진에 대한 비판적 시각이 존재하며, 로봇/반도체 관련 기대감이 일부 있으나 전반적인 분위기는 부정적.</t>
+          <t>대한광통신, 미국 광통신 관련주 강세 및 외인 수급 호조. 16000원 돌파 및 상승세 지속 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외국인 매도', '로봇', '반도체']</t>
+          <t>['광통신', '외인 수급', 'AI 관련주']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,46 +1936,46 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2050</v>
+        <v>7690</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+6.66%</t>
+          <t>+6.22%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.34</v>
+        <v>-0.09</v>
       </c>
       <c r="E17" t="n">
-        <v>156</v>
+        <v>265</v>
       </c>
       <c r="F17" t="n">
-        <v>65</v>
+        <v>104</v>
       </c>
       <c r="G17" t="n">
-        <v>292</v>
+        <v>973</v>
       </c>
       <c r="H17" t="n">
-        <v>0.85</v>
+        <v>11.62</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1922</v>
+        <v>7240</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.51</v>
+        <v>11.71</v>
       </c>
       <c r="O17" t="n">
-        <v>21203000000</v>
+        <v>35503000000</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,20 +2006,20 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>단기 급등 후 하락 및 거래량 부진. 테마주 수혜 기대감 언급.</t>
+          <t>금호타이어, 신용등급 상향 및 5조 계약 성공 소식 기반 상승 기대. 공매도 대결 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['단기 급등', '거래량', '테마주']</t>
+          <t>['신용등급', '계약 성공', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1863000</v>
+        <v>1856000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+3.90%</t>
+          <t>+3.51%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F18" t="n">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G18" t="n">
-        <v>2596</v>
+        <v>2655</v>
       </c>
       <c r="H18" t="n">
         <v>50.67</v>
@@ -2082,7 +2082,7 @@
         <v>50.66</v>
       </c>
       <c r="O18" t="n">
-        <v>5316562000000</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>자사주 매입 마무리 및 외국인 매수 전환 기대감. 긍정적 전망 제시.</t>
+          <t>SK하이닉스, 자사주 매입 마무리 및 TSMC 실적 호조 기대. 단기 하락 후 상승 전환 가능성.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외국인 매수', '기대감']</t>
+          <t>['자사주 매입', 'TSMC', '수급']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2148,7 +2148,7 @@
         <v>173</v>
       </c>
       <c r="G19" t="n">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="H19" t="n">
         <v>23.65</v>
@@ -2234,13 +2234,13 @@
         <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="F20" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G20" t="n">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="H20" t="n">
         <v>0.33</v>
@@ -2326,13 +2326,13 @@
         <v>-0.04</v>
       </c>
       <c r="E21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H21" t="n">
         <v>7.54</v>
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>270000</v>
+        <v>2170</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>+0.46%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.04</v>
+        <v>-0.35</v>
       </c>
       <c r="E22" t="n">
-        <v>791</v>
+        <v>110</v>
       </c>
       <c r="F22" t="n">
-        <v>435</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>1677</v>
+        <v>202</v>
       </c>
       <c r="H22" t="n">
-        <v>46.81</v>
+        <v>4.91</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>269500</v>
+        <v>2160</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>46.85</v>
+        <v>5.26</v>
       </c>
       <c r="O22" t="n">
-        <v>3250193000000</v>
+        <v>7784000000</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,40 +2466,40 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>자사주 매수 및 배당 기대감 속 정치적 발언 혼재. 약보합 마감.</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['자사주 매수', '배당', '정치']</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2160</v>
+        <v>269500</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>-0.04</v>
       </c>
       <c r="E23" t="n">
-        <v>109</v>
+        <v>792</v>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>432</v>
       </c>
       <c r="G23" t="n">
-        <v>199</v>
+        <v>1689</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>46.81</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2160</v>
+        <v>269500</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>46.85</v>
       </c>
       <c r="O23" t="n">
-        <v>7281000000</v>
+        <v>3339025000000</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,29 +2558,29 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
+          <t>삼성전자, 자사주 15조 매수 소식에 기대감. 단기 급등 및 하락 가능성 혼재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
+          <t>['자사주 매수', '기대감', '단기 변동성']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2602,13 +2602,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F24" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G24" t="n">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>LH의 호남 반도체 설계 용역 발주 및 금호건설의 수주 가능성 언급. 일부 개별적인 급등 기대 및 주가 하락에 대한 불안감 혼재.</t>
+          <t>금호건설, 수주 기사에도 불구하고 조용한 시장 반응. '개잡주' 인식 및 투자 주의 의견.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['반도체 설계 용역', '수주', '주가 전망']</t>
+          <t>['수주', '시장 반응', '주가']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19610</v>
+        <v>19640</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.80%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2697,10 +2697,10 @@
         <v>148</v>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G25" t="n">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>141602000000</v>
+        <v>145720000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대차해지 동참 요청에도 불구하고 주가 하락. 투자 심리 위축.</t>
+          <t>대우건설, 대차해지 동참 요청 활발. 미국 투자 관련 기대감 표출.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차해지', '주가 하락', '투자 심리']</t>
+          <t>['대차해지', '미국 투자', '기대감']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,11 +2775,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3645</v>
+        <v>3635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.30%</t>
+          <t>-6.56%</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2789,10 +2789,10 @@
         <v>88</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G26" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H26" t="n">
         <v>1.54</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>53129000000</v>
+        <v>53974000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F27" t="n">
         <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H27" t="n">
         <v>0.07000000000000001</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-23.06%</t>
+          <t>-24.55%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F28" t="n">
         <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>10399000000</v>
+        <v>10599000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3062,13 +3062,13 @@
         <v>-0.32</v>
       </c>
       <c r="E29" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F29" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G29" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="H29" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_15.xlsx
+++ b/data/trending_integrated_20260910_15.xlsx
@@ -567,21 +567,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8180</v>
+        <v>8300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+43.26%</t>
+          <t>+45.36%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F2" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G2" t="n">
         <v>1678</v>
@@ -610,7 +610,7 @@
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>72055000000</v>
+        <v>72462000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 폐암학회 발표 및 FDA 임상 관련 대형 재료 기대. 매물 소진 및 주가 상승 전망.</t>
+          <t>페니트리움바이오, 폐암학회 글로벌 제약사 참여 및 임상 결과 발표 관련 기대감 고조. 다락손과의 접점 및 후속 연구 데이터 공개 예정.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['폐암학회', 'FDA 임상', '대형 재료']</t>
+          <t>['폐암학회', '임상', '후속 데이터']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G3" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="H3" t="n">
         <v>0.14</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>삼미금속, 창사 이래 최대 호재 언급 있으나 구체적인 근거 제시 부족. 그래핀 신소재 관련 기대감 일부 포함.</t>
+          <t>창사 이래 최대 호재 및 신소재 그래핀 관련 언급, 급등 기대감 표출. 그러나 단기 조정 및 프로그램 매매 관련 부정적 의견도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['그래핀', '신소재', '호재']</t>
+          <t>['그래핀', '호재', '조정']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F4" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G4" t="n">
-        <v>999</v>
+        <v>1048</v>
       </c>
       <c r="H4" t="n">
         <v>6.09</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>우리기술, 미국 신규 원전 건설 소식 기반 상승 기대. 대장주 부각 및 공매도 관련 언급.</t>
+          <t>우리기술, 미국 신규 원전 건설 소식 및 원전 섹터 강세 언급. 2만원 목표 가격 제시하며 긍정적 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['원전주', '미국 신규 원전', '대장주']</t>
+          <t>['원전', '미국 신규 건설', '목표 가격']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14540</v>
+        <v>3660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+21.27%</t>
+          <t>+21.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>497</v>
+        <v>83</v>
       </c>
       <c r="F5" t="n">
-        <v>275</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>621</v>
+        <v>77</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>11990</v>
+        <v>3015</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>319856000000</v>
+        <v>28779000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -902,60 +902,60 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>흥구석유, 유가 급등 가능성에 기반한 상승 기대. 이란 관련 지정학적 리스크 언급.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가 급등', '지정학적 리스크', '이란']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3615</v>
+        <v>14510</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+19.90%</t>
+          <t>+21.02%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>502</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>276</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>627</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3015</v>
+        <v>11990</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>28509000000</v>
+        <v>321418000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,60 +994,60 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
+          <t>흥구석유, 유가 급등 가능성에 기반한 상승 기대. 이란 관련 지정학적 리스크 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['목표가', '단기과열', '주가조작']</t>
+          <t>['유가 급등', '지정학적 리스크', '이란']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12830</v>
+        <v>153500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.27%</t>
+          <t>+11.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>199</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>1085</v>
       </c>
       <c r="H7" t="n">
-        <v>4.37</v>
+        <v>15.65</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11530</v>
+        <v>138000</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.63</v>
+        <v>15.25</v>
       </c>
       <c r="O7" t="n">
-        <v>101161000000</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>SK이노베이션, 유가 급등 및 JP모건 대량 매수 관련 긍정적 언급 있으나, 주가 미반영 및 원유로 인한 상승 한계 지적.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['유가', 'JP모건', '원유']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>153500</v>
+        <v>12740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.23%</t>
+          <t>+10.49%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>444</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>200</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>1088</v>
+        <v>56</v>
       </c>
       <c r="H8" t="n">
-        <v>15.65</v>
+        <v>4.37</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>138000</v>
+        <v>11530</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>15.25</v>
+        <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>101344000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>유가 폭등으로 인한 기대감과 프로그램 매수세가 있으나, 원유 관련 주가 상승에 대한 의구심과 주가 하락 패턴에 대한 우려도 공존.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['유가', '프로그램 매수', '원유']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>넥스틸</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14460</v>
+        <v>2120</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+10.13%</t>
+          <t>+10.30%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.53</v>
+        <v>0.34</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>182</v>
+        <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.57</v>
+        <v>0.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13130</v>
+        <v>1922</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1251,10 +1251,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>0.51</v>
       </c>
       <c r="O9" t="n">
-        <v>122248000000</v>
+        <v>21809000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,68 +1270,68 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>중동 분쟁 관련 강관 수요 증가 기대감 속 주가 등락 반복, 재무제표 기반 목표가 논의.</t>
+          <t>강동씨앤엘, 새만금 소식 및 반도체 관련 긍정적 언급 있으나, 자전거래 및 기타법인 매도 등으로 인한 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['중동', '강관', '재무재표']</t>
+          <t>['새만금', '자전거래', '기타법인']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>092790</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2185</v>
+        <v>14370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+9.25%</t>
+          <t>+9.44%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>763</v>
+        <v>107</v>
       </c>
       <c r="F10" t="n">
-        <v>330</v>
+        <v>69</v>
       </c>
       <c r="G10" t="n">
-        <v>759</v>
+        <v>187</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>13130</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>975314000000</v>
+        <v>122791000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호, 높은 변동성과 투자 주의 의견 다수. 단기 급등 후 하락 가능성 언급.</t>
+          <t>중동 분쟁 관련 강관 수요 증가 기대감 속 주가 등락 반복, 재무제표 기반 목표가 논의.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['스팩주', '변동성', '주의']</t>
+          <t>['중동', '강관', '재무재표']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,51 +1379,51 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0197V0</t>
+          <t>092790</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2085</v>
+        <v>31100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+8.48%</t>
+          <t>+8.17%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>297</v>
+        <v>171</v>
       </c>
       <c r="H11" t="n">
-        <v>0.85</v>
+        <v>12.31</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1922</v>
+        <v>28750</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0.51</v>
+        <v>12.14</v>
       </c>
       <c r="O11" t="n">
-        <v>21622000000</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1454,60 +1454,60 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>단기 급등 후 하락 및 거래량 부진. 테마주 수혜 기대감 언급.</t>
+          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['단기 급등', '거래량', '테마주']</t>
+          <t>['외국인 매도', '개인 매수', '차익실현']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>흥아해운</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31100</v>
+        <v>1901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+8.17%</t>
+          <t>+8.01%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="H12" t="n">
-        <v>12.31</v>
+        <v>2.12</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>28750</v>
+        <v>1760</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>12.14</v>
+        <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>199001000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,68 +1546,68 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외국인 매도세 둔화 속 개인 매수세 전환에 따른 주가 변동성 발생. 단기적 반등 및 횡보 구간 예상.</t>
+          <t>종가 급락 및 기대감 저하. 단기 반등 및 종가 배팅 가능성 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외국인 매도', '개인 매수', '차익실현']</t>
+          <t>['종가', '반등', '기대감']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>003280</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>흥아해운</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1900</v>
+        <v>3925</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+7.95%</t>
+          <t>+7.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.05</v>
+        <v>-1.62</v>
       </c>
       <c r="E13" t="n">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="F13" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H13" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1760</v>
+        <v>3640</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1619,10 +1619,10 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.07</v>
+        <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>198524000000</v>
+        <v>151638000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1638,60 +1638,60 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>종가 급락 및 기대감 저하. 단기 반등 및 종가 배팅 가능성 언급.</t>
+          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['종가', '반등', '기대감']</t>
+          <t>['투기과열', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>003280</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3915</v>
+        <v>14740</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+7.55%</t>
+          <t>+7.59%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.62</v>
+        <v>1.34</v>
       </c>
       <c r="E14" t="n">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>246</v>
+        <v>715</v>
       </c>
       <c r="H14" t="n">
-        <v>1.57</v>
+        <v>2.89</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3640</v>
+        <v>13700</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.19</v>
+        <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>150888000000</v>
+        <v>117418000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,29 +1730,29 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>투기과열종목 회피, 6G 통신 및 광통신 이슈 기반 상승 기대감.</t>
+          <t>대한광통신, 미국 광통신 섹터 강세 및 외국인 수급 개선 기대감 형성. AI 관련주로도 분류되며 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['투기과열', '6G', '광통신']</t>
+          <t>['광통신', '외국인 수급', 'AI']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>-1.03</v>
       </c>
       <c r="E15" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F15" t="n">
         <v>69</v>
       </c>
       <c r="G15" t="n">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="H15" t="n">
         <v>15.68</v>
@@ -1851,39 +1851,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14590</v>
+        <v>7680</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+6.50%</t>
+          <t>+6.08%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.34</v>
+        <v>-0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>171</v>
+        <v>287</v>
       </c>
       <c r="F16" t="n">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="G16" t="n">
-        <v>706</v>
+        <v>1035</v>
       </c>
       <c r="H16" t="n">
-        <v>2.89</v>
+        <v>11.62</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13700</v>
+        <v>7240</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1895,10 +1895,10 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>11.71</v>
       </c>
       <c r="O16" t="n">
-        <v>114478000000</v>
+        <v>41434000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,20 +1914,20 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신 관련주 강세 및 외인 수급 호조. 16000원 돌파 및 상승세 지속 전망.</t>
+          <t>금호타이어, 신용등급 A2+ 부여 및 기업어음(CP) 관련 긍정적 분석 제시. 장춘공장 확장, 5조 계약 성공 등 구체적 호재 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '외인 수급', 'AI 관련주']</t>
+          <t>['신용등급', '기업어음', '계약']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7690</v>
+        <v>2260</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+6.22%</t>
+          <t>+4.63%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.09</v>
+        <v>-0.35</v>
       </c>
       <c r="E17" t="n">
-        <v>265</v>
+        <v>109</v>
       </c>
       <c r="F17" t="n">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>973</v>
+        <v>203</v>
       </c>
       <c r="H17" t="n">
-        <v>11.62</v>
+        <v>4.91</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>7240</v>
+        <v>2160</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1987,10 +1987,10 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>11.71</v>
+        <v>5.26</v>
       </c>
       <c r="O17" t="n">
-        <v>35503000000</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2006,68 +2006,68 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>금호타이어, 신용등급 상향 및 5조 계약 성공 소식 기반 상승 기대. 공매도 대결 언급.</t>
+          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['신용등급', '계약 성공', '공매도']</t>
+          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1856000</v>
+        <v>2075</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+3.51%</t>
+          <t>+3.75%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>794</v>
+        <v>777</v>
       </c>
       <c r="F18" t="n">
-        <v>456</v>
+        <v>337</v>
       </c>
       <c r="G18" t="n">
-        <v>2655</v>
+        <v>788</v>
       </c>
       <c r="H18" t="n">
-        <v>50.67</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1793000</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2079,10 +2079,10 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>50.66</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>976359000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,20 +2098,20 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SK하이닉스, 자사주 매입 마무리 및 TSMC 실적 호조 기대. 단기 하락 후 상승 전환 가능성.</t>
+          <t>엔에이치스팩34호, 단기 급등 후 하락 가능성 및 종가 예측 관련 혼재된 의견 제시. 스팩주의 일반적 결말 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'TSMC', '수급']</t>
+          <t>['스팩주', '급락 가능성', '종가 예측']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>0197V0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>91700</v>
+        <v>1853000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+2.46%</t>
+          <t>+3.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>292</v>
+        <v>788</v>
       </c>
       <c r="F19" t="n">
-        <v>173</v>
+        <v>444</v>
       </c>
       <c r="G19" t="n">
-        <v>1004</v>
+        <v>2664</v>
       </c>
       <c r="H19" t="n">
-        <v>23.65</v>
+        <v>50.67</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>89500</v>
+        <v>1793000</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2171,10 +2171,10 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>23.61</v>
+        <v>50.66</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>8069468000000</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2190,20 +2190,20 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 관련 호재 및 웨스팅하우스 지분 인수 가능성. 긍정적 전망 우세.</t>
+          <t>SK하이닉스, 자사주 매입 마무리 및 외인 매수 전환 기대감 형성. TSMC 실적 호조 언급. 다만, 마녀의 날 영향으로 인한 단기 변동성 가능성 존재.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '웨스팅하우스', '호재']</t>
+          <t>['자사주 매입', '외인 매수', 'TSMC']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,46 +2212,46 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30300</v>
+        <v>91700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="F20" t="n">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="G20" t="n">
-        <v>614</v>
+        <v>993</v>
       </c>
       <c r="H20" t="n">
-        <v>0.33</v>
+        <v>23.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>29750</v>
+        <v>89500</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.31</v>
+        <v>23.61</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2282,20 +2282,20 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2대 주주 한국산업은행의 존재가 언급되었으나, 급격한 주가 하락과 프로그램 매매에 대한 불신이 존재하며 향후 하락 가능성에 대한 전망이 제기됨.</t>
+          <t>미국 원전 건설 수주 기대감 속 최대 호재 언급, JP모건 리포트 등 긍정적 분석 기반. 다만, 공매도 관련 언급 및 가격 변동성 관련 부정적 심리도 혼재.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['한국산업은행', '프로그램 매매', '주가 하락']</t>
+          <t>['원전', '수주', '리포트']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,46 +2304,46 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23200</v>
+        <v>30300</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>92</v>
+        <v>353</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="G21" t="n">
-        <v>109</v>
+        <v>626</v>
       </c>
       <c r="H21" t="n">
-        <v>7.54</v>
+        <v>0.33</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>22900</v>
+        <v>29750</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>7.58</v>
+        <v>0.31</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2374,60 +2374,60 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>자사주 매입 소각 가능성으로 인한 주가 상승 기대. 유통 물량 거래 활발.</t>
+          <t>주가 급락 및 '탕후루' 비유 등 부정적 심리 강세. 2대 주주 산업은행 언급 및 향후 상승 기대도 있으나, 단기 급락에 대한 실망감 및 매도 심리 우세.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '주주환원']</t>
+          <t>['급락', '탕후루', '매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2170</v>
+        <v>23200</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.35</v>
+        <v>-0.04</v>
       </c>
       <c r="E22" t="n">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="H22" t="n">
-        <v>4.91</v>
+        <v>7.54</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2160</v>
+        <v>22900</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.26</v>
+        <v>7.58</v>
       </c>
       <c r="O22" t="n">
-        <v>7784000000</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 기대감 속 유증 발표 및 주가 변동성 확대. 경영권 분쟁 가능성.</t>
+          <t>자사주 매입 소각 가능성으로 인한 주가 상승 기대. 유통 물량 거래 활발.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['M&amp;A', '유증', '경영권 분쟁']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>269500</v>
+        <v>15640</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>792</v>
+        <v>139</v>
       </c>
       <c r="F23" t="n">
-        <v>432</v>
+        <v>83</v>
       </c>
       <c r="G23" t="n">
-        <v>1689</v>
+        <v>560</v>
       </c>
       <c r="H23" t="n">
-        <v>46.81</v>
+        <v>0</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>269500</v>
+        <v>15650</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>46.85</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3339025000000</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -2558,20 +2558,20 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>삼성전자, 자사주 15조 매수 소식에 기대감. 단기 급등 및 하락 가능성 혼재.</t>
+          <t>반도체 설계 용역 발주 및 수주 잔고 흑자 관련 긍정적 언급. 건설 사업 확대 뉴스 및 주가 부양 기대감 있으나, '개잡주' 등 부정적 인식도 혼재.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['자사주 매수', '기대감', '단기 변동성']</t>
+          <t>['수주', '건설', '흑자']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,38 +2580,38 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15640</v>
+        <v>269000</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>134</v>
+        <v>787</v>
       </c>
       <c r="F24" t="n">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="G24" t="n">
-        <v>554</v>
+        <v>1683</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>46.81</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>15650</v>
+        <v>269500</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>46.85</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>5628730000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,20 +2650,20 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>금호건설, 수주 기사에도 불구하고 조용한 시장 반응. '개잡주' 인식 및 투자 주의 의견.</t>
+          <t>삼성전자, 자사주 15조 매수 및 배당 소식으로 기대감 형성. 그러나 일부에서는 27만원 돌파 여부 및 장막판 급락 가능성 제기.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['수주', '시장 반응', '주가']</t>
+          <t>['자사주 매수', '배당', '기대감']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19640</v>
+        <v>19750</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-1.10%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F25" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G25" t="n">
-        <v>582</v>
+        <v>612</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>145720000000</v>
+        <v>160452000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대우건설, 대차해지 동참 요청 활발. 미국 투자 관련 기대감 표출.</t>
+          <t>대우건설, 대차거래 해지 동참 독려 및 2만원 고지 돌파 기대감 형성. 미국 투자 관련 호재 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차해지', '미국 투자', '기대감']</t>
+          <t>['대차해지', '미국 투자', '호재']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3635</v>
+        <v>3620</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.56%</t>
+          <t>-6.94%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="H26" t="n">
         <v>1.54</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>53974000000</v>
+        <v>54291000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>-0.01</v>
       </c>
       <c r="E27" t="n">
+        <v>76</v>
+      </c>
+      <c r="F27" t="n">
+        <v>47</v>
+      </c>
+      <c r="G27" t="n">
         <v>74</v>
-      </c>
-      <c r="F27" t="n">
-        <v>46</v>
-      </c>
-      <c r="G27" t="n">
-        <v>73</v>
       </c>
       <c r="H27" t="n">
         <v>0.07000000000000001</v>
@@ -2910,7 +2910,7 @@
         <v>0.08</v>
       </c>
       <c r="O27" t="n">
-        <v>840000000</v>
+        <v>868000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2959,24 +2959,24 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-24.55%</t>
+          <t>-24.22%</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G28" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>10599000000</v>
+        <v>10671000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3051,24 +3051,24 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-43.15%</t>
+          <t>-45.16%</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>-0.32</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F29" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G29" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H29" t="n">
         <v>5.86</v>
@@ -3094,7 +3094,7 @@
         <v>6.18</v>
       </c>
       <c r="O29" t="n">
-        <v>1096000000</v>
+        <v>1145000000</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260910_15.xlsx
+++ b/data/trending_integrated_20260910_15.xlsx
@@ -581,10 +581,10 @@
         <v>329</v>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>1678</v>
+        <v>1706</v>
       </c>
       <c r="H2" t="n">
         <v>1.17</v>
@@ -610,7 +610,7 @@
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>72462000000</v>
+        <v>72474000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 폐암학회 글로벌 제약사 참여 및 임상 결과 발표 관련 기대감 고조. 다락손과의 접점 및 후속 연구 데이터 공개 예정.</t>
+          <t>세계 폐암학회 발표 임상 결과 기대감 고조. 글로벌 제약사 참여 및 후속 연구 데이터 발표 예정.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['폐암학회', '임상', '후속 데이터']</t>
+          <t>['폐암학회', '임상', '연구 데이터']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H3" t="n">
         <v>0.14</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 및 신소재 그래핀 관련 언급, 급등 기대감 표출. 그러나 단기 조정 및 프로그램 매매 관련 부정적 의견도 존재.</t>
+          <t>역대 최대 호재와 그래핀 신소재 기대감 속에서 프로그램 매수 전환 가능성 관찰.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['그래핀', '호재', '조정']</t>
+          <t>['최대 호재', '그래핀', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14380</v>
+        <v>14600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.76%</t>
+          <t>+23.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.45</v>
       </c>
       <c r="E4" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F4" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G4" t="n">
-        <v>1048</v>
+        <v>1069</v>
       </c>
       <c r="H4" t="n">
         <v>6.09</v>
@@ -794,7 +794,7 @@
         <v>5.64</v>
       </c>
       <c r="O4" t="n">
-        <v>246464000000</v>
+        <v>249986000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>28779000000</v>
+        <v>28788000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -946,13 +946,13 @@
         <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>502</v>
+        <v>320</v>
       </c>
       <c r="F6" t="n">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="G6" t="n">
-        <v>627</v>
+        <v>380</v>
       </c>
       <c r="H6" t="n">
         <v>0.03</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>321418000000</v>
+        <v>321486000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>흥구석유, 유가 급등 가능성에 기반한 상승 기대. 이란 관련 지정학적 리스크 언급.</t>
+          <t>높은 변동성 속 주가조작 의혹 제기. 유가 변동 및 프로그램 매수 등 혼조세.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유가 급등', '지정학적 리스크', '이란']</t>
+          <t>['변동성', '주가조작', '유가']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F7" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>1085</v>
+        <v>1098</v>
       </c>
       <c r="H7" t="n">
         <v>15.65</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>SK이노베이션, 유가 급등 및 JP모건 대량 매수 관련 긍정적 언급 있으나, 주가 미반영 및 원유로 인한 상승 한계 지적.</t>
+          <t>유가 폭등에 따른 기대감과 함께 외국인 매수세가 관찰되나, 주가 하락에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유가', 'JP모건', '원유']</t>
+          <t>['유가', '외국인 매수', '주가 하락']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1162,7 +1162,7 @@
         <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>101344000000</v>
+        <v>101359000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1222,13 +1222,13 @@
         <v>0.34</v>
       </c>
       <c r="E9" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H9" t="n">
         <v>0.85</v>
@@ -1254,7 +1254,7 @@
         <v>0.51</v>
       </c>
       <c r="O9" t="n">
-        <v>21809000000</v>
+        <v>21815000000</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 새만금 소식 및 반도체 관련 긍정적 언급 있으나, 자전거래 및 기타법인 매도 등으로 인한 하락 우려 제기.</t>
+          <t>테마주로서의 불확실성 및 자전거래 의혹. 반도체 관련 긍정적 뉴스에도 불구하고 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['새만금', '자전거래', '기타법인']</t>
+          <t>['테마주', '자전거래', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F10" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G10" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="H10" t="n">
         <v>0.57</v>
@@ -1346,7 +1346,7 @@
         <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>122791000000</v>
+        <v>122799000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1406,13 +1406,13 @@
         <v>0.17</v>
       </c>
       <c r="E11" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
         <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H11" t="n">
         <v>12.31</v>
@@ -1498,13 +1498,13 @@
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="H12" t="n">
         <v>2.12</v>
@@ -1530,7 +1530,7 @@
         <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>199001000000</v>
+        <v>199040000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>종가 급락 및 기대감 저하. 단기 반등 및 종가 배팅 가능성 언급.</t>
+          <t>주가 급락 후 반등 기대감 속 혼조세. 일부 투자자는 매수 고려, 일부는 부정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['종가', '반등', '기대감']</t>
+          <t>['주가', '반등', '매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>-1.62</v>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="H13" t="n">
         <v>1.57</v>
@@ -1622,7 +1622,7 @@
         <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>151638000000</v>
+        <v>151673000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1682,13 +1682,13 @@
         <v>1.34</v>
       </c>
       <c r="E14" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F14" t="n">
         <v>86</v>
       </c>
       <c r="G14" t="n">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="H14" t="n">
         <v>2.89</v>
@@ -1714,7 +1714,7 @@
         <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>117418000000</v>
+        <v>117550000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신 섹터 강세 및 외국인 수급 개선 기대감 형성. AI 관련주로도 분류되며 상승 추세 전망.</t>
+          <t>미국 광통신 관련주 동반 강세 속 상승 추세. 외인 수급 및 AI 관련주로서의 잠재력 주목.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', '외국인 수급', 'AI']</t>
+          <t>['광통신', 'AI', '외인 수급']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,10 +1774,10 @@
         <v>-1.03</v>
       </c>
       <c r="E15" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G15" t="n">
         <v>358</v>
@@ -1866,13 +1866,13 @@
         <v>-0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F16" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G16" t="n">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="H16" t="n">
         <v>11.62</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>금호타이어, 신용등급 A2+ 부여 및 기업어음(CP) 관련 긍정적 분석 제시. 장춘공장 확장, 5조 계약 성공 등 구체적 호재 언급.</t>
+          <t>신용등급 상향(A2+) 및 5조 계약 성공 확정 등 긍정적 재료 부각. 공매도와의 대결 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['신용등급', '기업어음', '계약']</t>
+          <t>['신용등급', '계약', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1964,7 +1964,7 @@
         <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H17" t="n">
         <v>4.91</v>
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>777</v>
+        <v>637</v>
       </c>
       <c r="F18" t="n">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="G18" t="n">
-        <v>788</v>
+        <v>654</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>976359000000</v>
+        <v>976416000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호, 단기 급등 후 하락 가능성 및 종가 예측 관련 혼재된 의견 제시. 스팩주의 일반적 결말 언급.</t>
+          <t>스팩주의 특징적인 급등락 양상. 고가 매수 후 손실 발생에 대한 불안감 및 투매 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['스팩주', '급락 가능성', '종가 예측']</t>
+          <t>['스팩주', '급등락', '손실']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="F19" t="n">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G19" t="n">
-        <v>2664</v>
+        <v>2702</v>
       </c>
       <c r="H19" t="n">
         <v>50.67</v>
@@ -2174,7 +2174,7 @@
         <v>50.66</v>
       </c>
       <c r="O19" t="n">
-        <v>8069468000000</v>
+        <v>8084456000000</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SK하이닉스, 자사주 매입 마무리 및 외인 매수 전환 기대감 형성. TSMC 실적 호조 언급. 다만, 마녀의 날 영향으로 인한 단기 변동성 가능성 존재.</t>
+          <t>자사주 매입 종료 기대감 속 리밸런싱 영향으로 인한 단기 변동성. 외인 매수 전환 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['자사주 매입', '외인 매수', 'TSMC']</t>
+          <t>['자사주 매입', '리밸런싱', '외인']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F20" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G20" t="n">
-        <v>993</v>
+        <v>1014</v>
       </c>
       <c r="H20" t="n">
         <v>23.65</v>
@@ -2326,13 +2326,13 @@
         <v>0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F21" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G21" t="n">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="H21" t="n">
         <v>0.33</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>주가 급락 및 '탕후루' 비유 등 부정적 심리 강세. 2대 주주 산업은행 언급 및 향후 상승 기대도 있으나, 단기 급락에 대한 실망감 및 매도 심리 우세.</t>
+          <t>2대 주주 한국산업은행에 대한 언급과 함께 단기적인 주가 등락에 대한 의견 교차.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['급락', '탕후루', '매도']</t>
+          <t>['2대 주주', '한국산업은행', '주가 등락']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.04</v>
       </c>
       <c r="E22" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
         <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H22" t="n">
         <v>7.54</v>
@@ -2510,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G23" t="n">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="F24" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G24" t="n">
-        <v>1683</v>
+        <v>1751</v>
       </c>
       <c r="H24" t="n">
         <v>46.81</v>
@@ -2634,7 +2634,7 @@
         <v>46.85</v>
       </c>
       <c r="O24" t="n">
-        <v>5628730000000</v>
+        <v>5628908000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,16 +2650,16 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>삼성전자, 자사주 15조 매수 및 배당 소식으로 기대감 형성. 그러나 일부에서는 27만원 돌파 여부 및 장막판 급락 가능성 제기.</t>
+          <t>자사주 15조 매수 발표 호재, 그러나 정치적 이슈 및 환율 변동성으로 인한 혼조세.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['자사주 매수', '배당', '기대감']</t>
+          <t>['자사주 매수', '호재', '환율']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2694,13 +2694,13 @@
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F25" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G25" t="n">
-        <v>612</v>
+        <v>645</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>160452000000</v>
+        <v>160515000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>대우건설, 대차거래 해지 동참 독려 및 2만원 고지 돌파 기대감 형성. 미국 투자 관련 호재 언급.</t>
+          <t>대차 해지 운동 동참 독려 속 20000 고지 돌파 기대감 형성. 미국 투자 관련 긍정적 언급.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['대차해지', '미국 투자', '호재']</t>
+          <t>['대차 해지', '운동', '20000 고지']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2786,10 +2786,10 @@
         <v>-0.54</v>
       </c>
       <c r="E26" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G26" t="n">
         <v>215</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>54291000000</v>
+        <v>54313000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
         <v>0.08</v>
       </c>
       <c r="O27" t="n">
-        <v>868000000</v>
+        <v>869000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F28" t="n">
         <v>44</v>
       </c>
       <c r="G28" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>10671000000</v>
+        <v>10672000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3062,13 +3062,13 @@
         <v>-0.32</v>
       </c>
       <c r="E29" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G29" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H29" t="n">
         <v>5.86</v>
@@ -3094,7 +3094,7 @@
         <v>6.18</v>
       </c>
       <c r="O29" t="n">
-        <v>1145000000</v>
+        <v>1146000000</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>

--- a/data/trending_integrated_20260910_15.xlsx
+++ b/data/trending_integrated_20260910_15.xlsx
@@ -584,7 +584,7 @@
         <v>119</v>
       </c>
       <c r="G2" t="n">
-        <v>1706</v>
+        <v>1712</v>
       </c>
       <c r="H2" t="n">
         <v>1.17</v>
@@ -610,7 +610,7 @@
         <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>72474000000</v>
+        <v>72504000000</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H3" t="n">
         <v>0.14</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>역대 최대 호재와 그래핀 신소재 기대감 속에서 프로그램 매수 전환 가능성 관찰.</t>
+          <t>삼미금속, 그래핀 신소재 관련 호재 및 12500원 이상 마감 기대감 형성. 조정장 속 분할 매수 전략 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['최대 호재', '그래핀', '프로그램 매수']</t>
+          <t>['그래핀', '신소재']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -768,7 +768,7 @@
         <v>123</v>
       </c>
       <c r="G4" t="n">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="H4" t="n">
         <v>6.09</v>
@@ -794,7 +794,7 @@
         <v>5.64</v>
       </c>
       <c r="O4" t="n">
-        <v>249986000000</v>
+        <v>250074000000</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -854,13 +854,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>28788000000</v>
+        <v>28791000000</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -946,13 +946,13 @@
         <v>0.03</v>
       </c>
       <c r="E6" t="n">
-        <v>320</v>
+        <v>502</v>
       </c>
       <c r="F6" t="n">
-        <v>188</v>
+        <v>276</v>
       </c>
       <c r="G6" t="n">
-        <v>380</v>
+        <v>637</v>
       </c>
       <c r="H6" t="n">
         <v>0.03</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>321486000000</v>
+        <v>321559000000</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>높은 변동성 속 주가조작 의혹 제기. 유가 변동 및 프로그램 매수 등 혼조세.</t>
+          <t>흥구석유, 유가 급등 가능성에 대한 기대감과 함께 프로그램 매수세 및 외인 포지션 주목. 이란 유조선 피격 소식 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['변동성', '주가조작', '유가']</t>
+          <t>['유가', '브렌트유', '이란']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1044,7 +1044,7 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H7" t="n">
         <v>15.65</v>
@@ -1162,7 +1162,7 @@
         <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>101359000000</v>
+        <v>101365000000</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1222,13 +1222,13 @@
         <v>0.34</v>
       </c>
       <c r="E9" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F9" t="n">
         <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="H9" t="n">
         <v>0.85</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>테마주로서의 불확실성 및 자전거래 의혹. 반도체 관련 긍정적 뉴스에도 불구하고 투자 심리 위축.</t>
+          <t>강동씨앤엘, 지속적인 매수세 속에서 테마주 수혜 기대감 형성. 반도체 및 광주공항 건설 관련 내용 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['테마주', '자전거래', '반도체']</t>
+          <t>['테마주', '반도체']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1320,7 +1320,7 @@
         <v>73</v>
       </c>
       <c r="G10" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H10" t="n">
         <v>0.57</v>
@@ -1346,7 +1346,7 @@
         <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>122799000000</v>
+        <v>122807000000</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1498,13 +1498,13 @@
         <v>0.05</v>
       </c>
       <c r="E12" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H12" t="n">
         <v>2.12</v>
@@ -1530,7 +1530,7 @@
         <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>199040000000</v>
+        <v>199046000000</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1596,7 +1596,7 @@
         <v>71</v>
       </c>
       <c r="G13" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H13" t="n">
         <v>1.57</v>
@@ -1622,7 +1622,7 @@
         <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>151673000000</v>
+        <v>151747000000</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1682,13 +1682,13 @@
         <v>1.34</v>
       </c>
       <c r="E14" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G14" t="n">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="H14" t="n">
         <v>2.89</v>
@@ -1714,7 +1714,7 @@
         <v>1.55</v>
       </c>
       <c r="O14" t="n">
-        <v>117550000000</v>
+        <v>117584000000</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1774,13 +1774,13 @@
         <v>-1.03</v>
       </c>
       <c r="E15" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F15" t="n">
         <v>70</v>
       </c>
       <c r="G15" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H15" t="n">
         <v>15.68</v>
@@ -1866,13 +1866,13 @@
         <v>-0.09</v>
       </c>
       <c r="E16" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F16" t="n">
         <v>115</v>
       </c>
       <c r="G16" t="n">
-        <v>1033</v>
+        <v>1049</v>
       </c>
       <c r="H16" t="n">
         <v>11.62</v>
@@ -1898,7 +1898,7 @@
         <v>11.71</v>
       </c>
       <c r="O16" t="n">
-        <v>41434000000</v>
+        <v>41435000000</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>신용등급 상향(A2+) 및 5조 계약 성공 확정 등 긍정적 재료 부각. 공매도와의 대결 언급.</t>
+          <t>금호타이어, CP 신용등급 A2+ 부여 소식과 함께 기업 정상화 기대감 형성. 27년 중국 시장 전망 및 5조 계약 성공 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['신용등급', '계약', '공매도']</t>
+          <t>['신용등급', '기업어음', '정상화']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.35</v>
       </c>
       <c r="E17" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F17" t="n">
         <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="H17" t="n">
         <v>4.91</v>
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>637</v>
+        <v>794</v>
       </c>
       <c r="F18" t="n">
-        <v>278</v>
+        <v>345</v>
       </c>
       <c r="G18" t="n">
-        <v>654</v>
+        <v>809</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>976416000000</v>
+        <v>976495000000</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>스팩주의 특징적인 급등락 양상. 고가 매수 후 손실 발생에 대한 불안감 및 투매 가능성 언급.</t>
+          <t>엔에이치스팩34호, 주가 변동성에 대한 투자자들의 희망과 절망이 교차하는 상황. 급락 가능성 및 7000원 이상 종가 기대 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['스팩주', '급등락', '손실']</t>
+          <t>['스팩주', '변동성']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2142,13 +2142,13 @@
         <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="F19" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G19" t="n">
-        <v>2702</v>
+        <v>2716</v>
       </c>
       <c r="H19" t="n">
         <v>50.67</v>
@@ -2174,7 +2174,7 @@
         <v>50.66</v>
       </c>
       <c r="O19" t="n">
-        <v>8084456000000</v>
+        <v>8098752000000</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2237,10 +2237,10 @@
         <v>298</v>
       </c>
       <c r="F20" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G20" t="n">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="H20" t="n">
         <v>23.65</v>
@@ -2326,13 +2326,13 @@
         <v>0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F21" t="n">
         <v>156</v>
       </c>
       <c r="G21" t="n">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="H21" t="n">
         <v>0.33</v>
@@ -2424,7 +2424,7 @@
         <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H22" t="n">
         <v>7.54</v>
@@ -2510,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F23" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G23" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>-0.04</v>
       </c>
       <c r="E24" t="n">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F24" t="n">
         <v>441</v>
       </c>
       <c r="G24" t="n">
-        <v>1751</v>
+        <v>1768</v>
       </c>
       <c r="H24" t="n">
         <v>46.81</v>
@@ -2634,7 +2634,7 @@
         <v>46.85</v>
       </c>
       <c r="O24" t="n">
-        <v>5628908000000</v>
+        <v>5628940000000</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>자사주 15조 매수 발표 호재, 그러나 정치적 이슈 및 환율 변동성으로 인한 혼조세.</t>
+          <t>삼성전자 자사주 15조 매수 및 배당 관련 소식 언급. 일부 투자자들의 기대감과 함께 3일 연속 보합세를 보이는 상황.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['자사주 매수', '호재', '환율']</t>
+          <t>['자사주 매수', '배당']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2694,13 +2694,13 @@
         <v>-0.21</v>
       </c>
       <c r="E25" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F25" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G25" t="n">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="H25" t="n">
         <v>10.64</v>
@@ -2726,7 +2726,7 @@
         <v>10.85</v>
       </c>
       <c r="O25" t="n">
-        <v>160515000000</v>
+        <v>160529000000</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2818,7 +2818,7 @@
         <v>2.08</v>
       </c>
       <c r="O26" t="n">
-        <v>54313000000</v>
+        <v>54361000000</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>47</v>
       </c>
       <c r="G27" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H27" t="n">
         <v>0.07000000000000001</v>
@@ -2910,7 +2910,7 @@
         <v>0.08</v>
       </c>
       <c r="O27" t="n">
-        <v>869000000</v>
+        <v>872000000</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2970,13 +2970,13 @@
         <v>0.38</v>
       </c>
       <c r="E28" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H28" t="n">
         <v>2.8</v>
@@ -3002,7 +3002,7 @@
         <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>10672000000</v>
+        <v>10677000000</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -3062,13 +3062,13 @@
         <v>-0.32</v>
       </c>
       <c r="E29" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F29" t="n">
         <v>55</v>
       </c>
       <c r="G29" t="n">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="H29" t="n">
         <v>5.86</v>
@@ -3094,7 +3094,7 @@
         <v>6.18</v>
       </c>
       <c r="O29" t="n">
-        <v>1146000000</v>
+        <v>1147000000</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
